--- a/reports/devops-jobs-israel-2026-W26.xlsx
+++ b/reports/devops-jobs-israel-2026-W26.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="515">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-22T12:21:54</t>
+    <t xml:space="preserve">2026-06-23T09:59:14</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8%</t>
+    <t xml:space="preserve">2.7%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -159,30 +159,33 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
   </si>
   <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution Architect</t>
   </si>
   <si>
@@ -510,6 +513,15 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Devops Engineer</t>
   </si>
   <si>
@@ -519,7 +531,7 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
   </si>
   <si>
     <t xml:space="preserve">Lightricks</t>
@@ -528,12 +540,6 @@
     <t xml:space="preserve">Jerusalem</t>
   </si>
   <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
   </si>
   <si>
@@ -582,6 +588,15 @@
     <t xml:space="preserve">2026-06-22</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
     <t xml:space="preserve">SessionCam</t>
   </si>
   <si>
@@ -594,24 +609,72 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4430430529</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharpies PRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sharpies-pro-4431207225</t>
   </si>
   <si>
     <t xml:space="preserve">Kela Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
   </si>
   <si>
+    <t xml:space="preserve">CodSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4430893634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-engineer-devops-at-teads-4431209410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer (Core)</t>
   </si>
   <si>
@@ -621,861 +684,762 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-core-at-island-4431638784</t>
   </si>
   <si>
-    <t xml:space="preserve">Planck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
+    <t xml:space="preserve">DevOps &amp; IT Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contguard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-manager-at-contguard-4427327416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4430560470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4430439283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4432073801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer%C2%A0-aws-at-comblack-4431673887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razor Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noma Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4428586431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist (36628)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4430455329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-team-leader-at-evoke-4431694215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stepscale.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-platform-engineer-at-stepscale-io-4432091419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-hyro-4418385319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-4399101600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teva Pharmaceuticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4429373530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (533457)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-533457-at-malamteam-4429959988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experience Linux Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galil Software Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experience-linux-engineer-at-galil-software-ltd-4430379128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4431715362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Fend Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-d-fend-solutions-4429992083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer (620127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpearUAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-620127-at-spearuav-4427344299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377765290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-controp-precision-technologies-ltd-4424404648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XM Cyber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoTraffic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-notraffic-4430412124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-16</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; IT Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contguard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-manager-at-contguard-4427327416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; CloudOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloudops-at-moveo-source-4427499835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4430439283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4431627578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer%C2%A0-aws-at-comblack-4431673887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razor Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4428586431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moovit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moovit-4431683310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist (36628)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4430455329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XM Cyber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-bridgify-4428851792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teva Pharmaceuticals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4428639232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4429373530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (533457)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-533457-at-malamteam-4429959988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experience Linux Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galil Software Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experience-linux-engineer-at-galil-software-ltd-4430379128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4429338126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-rafael-advanced-defense-systems-4429211666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-Fend Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-d-fend-solutions-4429992083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer (620127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpearUAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-620127-at-spearuav-4427344299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377765290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-controp-precision-technologies-ltd-4424404648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Project Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-project-manager-at-varonis-4431384600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4428945098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NoTraffic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-notraffic-4430412124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAAT Delivery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-haat-delivery-4426484215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Network Operations Center Engineer</t>
   </si>
   <si>
@@ -1488,9 +1452,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
   </si>
   <si>
@@ -1503,18 +1464,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
   </si>
   <si>
@@ -1551,6 +1500,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1560,12 +1518,12 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -1576,6 +1534,9 @@
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1727,7 +1688,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
@@ -1735,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1743,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -1751,7 +1712,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>700</v>
+        <v>716</v>
       </c>
     </row>
     <row r="10">
@@ -1759,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1823,7 +1784,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -1850,54 +1811,46 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>437</v>
+        <v>496</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1914,47 +1867,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B3" s="3">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="B6" s="3">
         <v>16</v>
@@ -1962,15 +1915,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>516</v>
+        <v>405</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>414</v>
+        <v>502</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -1978,7 +1931,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -1986,47 +1939,47 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>411</v>
+        <v>504</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>518</v>
+        <v>403</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>410</v>
+        <v>182</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>180</v>
+        <v>401</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>415</v>
+        <v>505</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -2034,10 +1987,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2062,13 +2015,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2">
@@ -2079,10 +2032,10 @@
         <v>38</v>
       </c>
       <c r="C2" s="3">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2091,88 +2044,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
-        <v>37.9</v>
+        <v>35.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.0</v>
+        <v>31.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.4</v>
+        <v>15.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>13.3</v>
+        <v>14.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2183,7 +2136,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -2256,7 +2209,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -2288,7 +2241,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -2317,15 +2270,15 @@
         <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>35</v>
@@ -2340,24 +2293,24 @@
         <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>35</v>
@@ -2372,7 +2325,7 @@
         <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
@@ -2381,15 +2334,15 @@
         <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>35</v>
@@ -2404,659 +2357,659 @@
         <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J7" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J12" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J16" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J20" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J21" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J22" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J24" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J25" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J26" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J27" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -3064,212 +3017,210 @@
         <v>45</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J30" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J33" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>164</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
@@ -3277,29 +3228,31 @@
         <v>165</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="J34" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
@@ -3307,10 +3260,10 @@
         <v>169</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
@@ -3318,13 +3271,13 @@
         <v>170</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>38</v>
@@ -3334,224 +3287,226 @@
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J36" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J37" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>189</v>
+        <v>37</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J41" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -3559,211 +3514,209 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="J46" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="J48" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>140</v>
+        <v>221</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>222</v>
+        <v>64</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>225</v>
+        <v>59</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="J50" s="3">
         <v>0</v>
@@ -3771,49 +3724,51 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>228</v>
+        <v>71</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>230</v>
+        <v>112</v>
       </c>
       <c r="J51" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
@@ -3823,39 +3778,37 @@
         <v>233</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>180</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="J53" s="3">
         <v>0</v>
@@ -3863,48 +3816,48 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>56</v>
+        <v>238</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="J54" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3914,27 +3867,27 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
@@ -3944,250 +3897,252 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="J56" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>63</v>
+        <v>246</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>58</v>
+        <v>249</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="J57" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>245</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>248</v>
+        <v>92</v>
       </c>
       <c r="J58" s="3">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>96</v>
+        <v>253</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>186</v>
+        <v>256</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="J61" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>140</v>
+        <v>263</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="J62" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>260</v>
+        <v>97</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>262</v>
+        <v>181</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>140</v>
+        <v>269</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="J64" s="3">
         <v>6</v>
@@ -4195,353 +4150,351 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>268</v>
+        <v>181</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>269</v>
+        <v>147</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>186</v>
+        <v>278</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>141</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>140</v>
+        <v>283</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="J69" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>283</v>
+        <v>141</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>238</v>
+        <v>286</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="J70" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>256</v>
+        <v>44</v>
       </c>
       <c r="J73" s="3">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>296</v>
+        <v>60</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="J74" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>96</v>
+        <v>299</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>248</v>
+        <v>128</v>
       </c>
       <c r="J75" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>300</v>
+        <v>64</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>301</v>
+        <v>189</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>195</v>
+        <v>302</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>302</v>
-      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
@@ -4549,24 +4502,24 @@
         <v>303</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>202</v>
+        <v>304</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>63</v>
+        <v>305</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>304</v>
+        <v>189</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>195</v>
+        <v>302</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>38</v>
@@ -4576,27 +4529,27 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
       <c r="J77" s="3">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>38</v>
@@ -4606,27 +4559,27 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>309</v>
+        <v>64</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>38</v>
@@ -4636,57 +4589,57 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>286</v>
+        <v>44</v>
       </c>
       <c r="J79" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="J80" s="3">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>63</v>
+        <v>316</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4696,190 +4649,190 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>63</v>
+        <v>319</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>321</v>
+        <v>166</v>
       </c>
       <c r="J83" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="J84" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>140</v>
+        <v>327</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>324</v>
+        <v>226</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>225</v>
+        <v>59</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="J85" s="3">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>45</v>
+        <v>329</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="J86" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>140</v>
+        <v>332</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>238</v>
+        <v>334</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="J87" s="3">
         <v>0</v>
@@ -4887,29 +4840,29 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="J88" s="3">
         <v>5</v>
@@ -4917,16 +4870,16 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>38</v>
@@ -4936,42 +4889,40 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J89" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>335</v>
+        <v>64</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>123</v>
+        <v>234</v>
       </c>
       <c r="J90" s="3">
         <v>4</v>
@@ -4979,46 +4930,46 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>339</v>
+        <v>257</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J91" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>341</v>
+        <v>45</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>343</v>
+        <v>208</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>38</v>
@@ -5028,10 +4979,10 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="J92" s="3">
         <v>6</v>
@@ -5039,19 +4990,19 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>345</v>
+        <v>141</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>346</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
@@ -5061,27 +5012,27 @@
         <v>347</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>322</v>
+        <v>141</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>191</v>
+        <v>348</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>348</v>
+        <v>203</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
@@ -5091,7 +5042,7 @@
         <v>349</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="J94" s="3">
         <v>6</v>
@@ -5099,203 +5050,205 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>351</v>
-      </c>
       <c r="C95" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>189</v>
+        <v>59</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="J95" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>355</v>
-      </c>
       <c r="I96" s="3" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J96" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>359</v>
-      </c>
       <c r="I97" s="3" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>361</v>
+        <v>203</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>296</v>
+        <v>60</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="J98" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>221</v>
+        <v>124</v>
       </c>
       <c r="J99" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>367</v>
-      </c>
       <c r="I100" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>281</v>
-      </c>
       <c r="D101" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
@@ -5305,29 +5258,31 @@
         <v>370</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="J101" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>371</v>
+        <v>267</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F102" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
@@ -5335,10 +5290,10 @@
         <v>372</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="J102" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -5349,13 +5304,13 @@
         <v>374</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
@@ -5365,7 +5320,7 @@
         <v>375</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="J103" s="3">
         <v>0</v>
@@ -5373,258 +5328,258 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>268</v>
+        <v>190</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>269</v>
+        <v>37</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J104" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>378</v>
+        <v>203</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J105" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="J106" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="D107" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="J107" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>387</v>
-      </c>
       <c r="C108" s="3" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="J108" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>389</v>
+        <v>293</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="J109" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>393</v>
+        <v>257</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F110" s="3"/>
+      <c r="F110" s="3" t="s">
+        <v>391</v>
+      </c>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="J110" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>395</v>
+        <v>290</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>251</v>
+        <v>393</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>238</v>
+        <v>71</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>396</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="J111" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>398</v>
+        <v>64</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>38</v>
@@ -5634,107 +5589,47 @@
         <v>23</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="J112" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>289</v>
+        <v>67</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>321</v>
+        <v>44</v>
       </c>
       <c r="J113" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="J114" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J115" s="3">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J115"/>
+  <autoFilter ref="A1:J113"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5848,8 +5743,6 @@
     <hyperlink ref="H111" r:id="rId110"/>
     <hyperlink ref="H112" r:id="rId111"/>
     <hyperlink ref="H113" r:id="rId112"/>
-    <hyperlink ref="H114" r:id="rId113"/>
-    <hyperlink ref="H115" r:id="rId114"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5857,9 +5750,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5891,13 +5784,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5905,18 +5798,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5924,18 +5817,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5943,18 +5836,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5962,18 +5855,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>234</v>
+        <v>141</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5981,18 +5874,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6000,18 +5893,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>96</v>
+        <v>235</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6019,18 +5912,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6038,18 +5931,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6057,18 +5950,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6076,18 +5969,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>359</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6095,18 +5988,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>373</v>
+        <v>329</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>374</v>
+        <v>330</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>238</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6114,18 +6007,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>377</v>
+        <v>333</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>378</v>
+        <v>334</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6133,18 +6026,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>379</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>386</v>
+        <v>141</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6152,18 +6045,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6171,11 +6064,30 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>391</v>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G17"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6192,6 +6104,7 @@
     <hyperlink ref="G14" r:id="rId13"/>
     <hyperlink ref="G15" r:id="rId14"/>
     <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6205,39 +6118,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -6245,31 +6158,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>358</v>
+        <v>404</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>413</v>
+        <v>353</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -6277,15 +6190,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -6293,7 +6206,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -6301,31 +6214,31 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -6338,7 +6251,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6347,7 +6260,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
@@ -6360,7 +6273,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6368,7 +6281,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -6376,15 +6289,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>57</v>
+        <v>189</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>191</v>
+        <v>58</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6392,7 +6305,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>251</v>
+        <v>159</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6400,7 +6313,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>324</v>
+        <v>257</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6408,7 +6321,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6416,7 +6329,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6424,7 +6337,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6432,7 +6345,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6440,7 +6353,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6448,7 +6361,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6456,7 +6369,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>178</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6464,7 +6377,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6485,16 +6398,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
@@ -6502,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3">
         <v>22.7</v>
@@ -6516,13 +6429,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -6530,13 +6443,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="C4" s="3">
-        <v>17.3</v>
+        <v>19.2</v>
       </c>
       <c r="D4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -6544,7 +6457,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" s="3">
         <v>10.9</v>
@@ -6558,13 +6471,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="C6" s="3">
-        <v>7.3</v>
+        <v>8.8</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6572,10 +6485,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -6586,10 +6499,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>6.2</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6600,13 +6513,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -6614,13 +6527,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>251</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3">
         <v>4.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6628,13 +6541,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>119</v>
+        <v>257</v>
       </c>
       <c r="C11" s="3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6642,13 +6555,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>191</v>
+        <v>120</v>
       </c>
       <c r="C12" s="3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6656,13 +6569,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>324</v>
+        <v>142</v>
       </c>
       <c r="C13" s="3">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6670,10 +6583,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>178</v>
+        <v>368</v>
       </c>
       <c r="C14" s="3">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6684,10 +6597,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C15" s="3">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -6698,10 +6611,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="C16" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6724,18 +6637,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>296</v>
+        <v>214</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6743,13 +6656,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4">
@@ -6757,10 +6670,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -6779,23 +6692,23 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" s="3">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6808,15 +6721,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6824,15 +6737,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>269</v>
+        <v>172</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6840,7 +6753,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6855,7 +6768,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6867,10 +6780,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6882,10 +6795,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6902,28 +6815,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6934,31 +6847,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>436</v>
+        <v>71</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4">
@@ -6966,31 +6879,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>91</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
@@ -6998,31 +6911,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="F5" s="3">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -7030,28 +6943,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F6" s="3">
         <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>44</v>
@@ -7062,31 +6975,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>454</v>
+        <v>159</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>455</v>
+        <v>422</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -7094,31 +7007,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>458</v>
+        <v>74</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F8" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>460</v>
+        <v>76</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -7126,31 +7039,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>73</v>
+        <v>445</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>69</v>
+        <v>291</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>455</v>
+        <v>422</v>
       </c>
       <c r="F9" s="3">
         <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>75</v>
+        <v>447</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -7158,28 +7071,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="F10" s="3">
         <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7190,31 +7103,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F11" s="3">
+        <v>40</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="F11" s="3">
-        <v>32</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -7222,31 +7135,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F12" s="3">
+        <v>32</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="F12" s="3">
-        <v>30</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>469</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>471</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -7254,31 +7167,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="F13" s="3">
         <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14">
@@ -7286,31 +7199,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>476</v>
+        <v>425</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>478</v>
+        <v>286</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F14" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>405</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
@@ -7318,31 +7231,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="F15" s="3">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>202</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16">
@@ -7350,31 +7263,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="F16" s="3">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17">
@@ -7382,31 +7295,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="F17" s="3">
         <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -7414,31 +7327,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>343</v>
+        <v>203</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="F18" s="3">
         <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>405</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -7446,31 +7359,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>499</v>
+        <v>180</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>431</v>
+        <v>486</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -7478,31 +7391,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>178</v>
+        <v>490</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="F20" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21">
@@ -7510,31 +7423,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>507</v>
+        <v>180</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="F21" s="3">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W26.xlsx
+++ b/reports/devops-jobs-israel-2026-W26.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-23T09:59:14</t>
+    <t xml:space="preserve">2026-06-24T09:47:41</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,15 +57,12 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7%</t>
+    <t xml:space="preserve">0.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0%</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -159,10 +156,13 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
     <t xml:space="preserve">Lead DevOps Engineer</t>
@@ -177,15 +177,9 @@
     <t xml:space="preserve">Senior Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution Architect</t>
   </si>
   <si>
@@ -255,400 +249,1054 @@
     <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps Engineer, Application Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, ELK/Elastic, Service Mesh, Kafka, RabbitMQ, Networking, Security, Argo CD, Observability, Crossplane, Flux/GitOps, Container Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7955819/?gh_jid=7955819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of AI Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Ansible, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4430717128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aws-devops-engineer-at-abra-4430316804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharpies PRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sharpies-pro-4431207225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razor Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4432510401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-logica-it-4429449489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4432276748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4430560470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4428586431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aran R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pardes Hana-Karkur, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-aran-r-d-4429840108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer [Contracting]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory Ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-contracting-at-theory-ventures-4432553221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4431766041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Security - AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-security-ai-platform-engineer-at-cato-networks-4416844175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4409726747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer%C2%A0-aws-at-comblack-4431673887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noma Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4429458777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teva Pharmaceuticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Maternity Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-maternity-leave-replacement-at-earnix-4431370720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4429373530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (533457)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-533457-at-malamteam-4429959988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4431715362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experience Linux Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galil Software Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experience-linux-engineer-at-galil-software-ltd-4430379128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4431218841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4432202668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Fend Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-d-fend-solutions-4429992083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoTraffic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-notraffic-4430412124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7818160&amp;gh_jid=7818160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of AI Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Ansible, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aws-devops-engineer-at-abra-4430316804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4430717128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4430430529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharpies PRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sharpies-pro-4431207225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4430893634</t>
+    <t xml:space="preserve">JFrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-cloud-architect-at-jfrog-4428560936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stepscale.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-platform-engineer-at-stepscale-io-4432091419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Cloud Engineer (DevOps)</t>
@@ -660,669 +1308,18 @@
     <t xml:space="preserve">Netanya, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-engineer-devops-at-teads-4431209410</t>
   </si>
   <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Core)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-core-at-island-4431638784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; IT Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contguard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-manager-at-contguard-4427327416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4430560470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4430439283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4432073801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer%C2%A0-aws-at-comblack-4431673887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razor Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noma Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4428586431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist (36628)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4430455329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-team-leader-at-evoke-4431694215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founding Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stepscale.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-platform-engineer-at-stepscale-io-4432091419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-hyro-4418385319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-4399101600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teva Pharmaceuticals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4429373530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (533457)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-533457-at-malamteam-4429959988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experience Linux Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galil Software Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experience-linux-engineer-at-galil-software-ltd-4430379128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4431715362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-Fend Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-d-fend-solutions-4429992083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer (620127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpearUAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-620127-at-spearuav-4427344299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4377765290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-controp-precision-technologies-ltd-4424404648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XM Cyber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NoTraffic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-notraffic-4430412124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anecdotes</t>
   </si>
   <si>
@@ -1356,6 +1353,21 @@
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support</t>
   </si>
   <si>
@@ -1389,6 +1401,21 @@
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Product Operations – Part-Time Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-product-operations-%E2%80%93-part-time-student-at-finout-4427681349</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Operations Engineer</t>
   </si>
   <si>
@@ -1401,6 +1428,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristocrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
+  </si>
+  <si>
     <t xml:space="preserve">Helpdesk Specialist</t>
   </si>
   <si>
@@ -1443,9 +1482,6 @@
     <t xml:space="preserve">Junior Network Operations Center Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
   </si>
   <si>
@@ -1464,66 +1500,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -1537,6 +1525,9 @@
   </si>
   <si>
     <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1688,7 +1679,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -1696,7 +1687,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -1704,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>716</v>
+        <v>734</v>
       </c>
     </row>
     <row r="10">
@@ -1720,7 +1711,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1736,7 +1727,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1745,26 +1736,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1773,23 +1764,23 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3">
         <v>36</v>
@@ -1808,23 +1799,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B3" s="3">
         <v>17</v>
@@ -1832,15 +1823,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1848,7 +1839,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>496</v>
+        <v>438</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1867,31 +1858,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B4" s="3">
         <v>21</v>
@@ -1899,39 +1890,39 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>502</v>
+        <v>395</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>499</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -1939,7 +1930,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>503</v>
+        <v>352</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
@@ -1947,7 +1938,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>504</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -1955,42 +1946,42 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>403</v>
+        <v>500</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2009,123 +2000,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3">
         <v>38</v>
       </c>
       <c r="C2" s="3">
-        <v>13.3</v>
+        <v>14.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>81</v>
       </c>
       <c r="C3" s="3">
-        <v>35.9</v>
+        <v>33.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.9</v>
+        <v>9.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.5</v>
+        <v>2.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.8</v>
+        <v>34.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2137,7 +2128,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2150,130 +2141,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J2" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J3" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J4" s="3">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -2281,31 +2272,31 @@
         <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -2313,1048 +2304,1046 @@
         <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J6" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="J8" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="J12" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J13" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="I14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J14" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="I15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J15" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="J16" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="I17" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J18" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="J19" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="J20" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="J21" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J22" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="I23" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J23" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="J24" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J25" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="J26" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="I27" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J27" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J28" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="I29" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J29" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="J30" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J31" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J32" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="3" t="s">
+      <c r="I33" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="J33" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="J34" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="I35" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J35" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="J36" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="I37" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J37" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="D38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="I38" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="J38" s="3">
         <v>2</v>
@@ -3362,361 +3351,365 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="G39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="3" t="s">
+      <c r="I39" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="J40" s="3">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G45" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>213</v>
+        <v>57</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>203</v>
+        <v>69</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F47" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G47" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>64</v>
+        <v>220</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="J50" s="3">
         <v>0</v>
@@ -3724,665 +3717,663 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>71</v>
+        <v>195</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>199</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="J51" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>141</v>
+        <v>226</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>234</v>
+        <v>43</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>235</v>
+        <v>140</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>238</v>
+        <v>140</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F55" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="G55" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>201</v>
+        <v>43</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>246</v>
+        <v>55</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>249</v>
+        <v>57</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G57" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>188</v>
+        <v>245</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>57</v>
+        <v>246</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>199</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J58" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>253</v>
+        <v>62</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="J59" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>262</v>
+        <v>181</v>
       </c>
       <c r="J61" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>263</v>
+        <v>62</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="J62" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>269</v>
+        <v>62</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>213</v>
+        <v>57</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="J64" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>272</v>
+        <v>140</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>147</v>
+        <v>264</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>234</v>
+        <v>165</v>
       </c>
       <c r="J65" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>203</v>
+        <v>268</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>59</v>
+        <v>264</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="J66" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>141</v>
+        <v>273</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>265</v>
+        <v>195</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>286</v>
+        <v>189</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="J70" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>198</v>
+        <v>287</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>59</v>
+        <v>264</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J72" s="3">
         <v>2</v>
@@ -4390,599 +4381,611 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>44</v>
+        <v>291</v>
       </c>
       <c r="J73" s="3">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>256</v>
+        <v>43</v>
       </c>
       <c r="J74" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>300</v>
+        <v>191</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>128</v>
+        <v>245</v>
       </c>
       <c r="J75" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="D76" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>304</v>
+        <v>236</v>
       </c>
       <c r="J76" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="J77" s="3">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="J78" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>198</v>
+        <v>287</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>59</v>
+        <v>264</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>44</v>
+        <v>305</v>
       </c>
       <c r="J79" s="3">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="J80" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>319</v>
+        <v>55</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F82" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G82" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="J82" s="3">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>141</v>
+        <v>314</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="J83" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>325</v>
+        <v>234</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F84" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G84" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="J84" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>327</v>
+        <v>62</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="J85" s="3">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F86" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="G86" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>334</v>
+        <v>228</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>64</v>
+        <v>325</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>336</v>
+        <v>227</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F88" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G88" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>124</v>
+        <v>327</v>
       </c>
       <c r="J88" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="J89" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>342</v>
+        <v>203</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F91" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G91" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="J91" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>45</v>
+        <v>333</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F92" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="J92" s="3">
         <v>6</v>
@@ -4990,337 +4993,335 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>141</v>
+        <v>336</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F93" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G93" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>141</v>
+        <v>339</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>203</v>
+        <v>341</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="J94" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>141</v>
+        <v>343</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>302</v>
+        <v>217</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>353</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J96" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>355</v>
+        <v>266</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>356</v>
+        <v>251</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>198</v>
+        <v>349</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>199</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="J97" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>359</v>
+        <v>253</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F98" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>352</v>
+      </c>
       <c r="G98" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="J98" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>361</v>
+        <v>266</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="J99" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>286</v>
+        <v>231</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="J100" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>367</v>
+        <v>266</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>369</v>
+        <v>231</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="J101" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>353</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="J102" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>373</v>
+        <v>266</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>203</v>
+        <v>349</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="J103" s="3">
         <v>0</v>
@@ -5328,92 +5329,92 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>373</v>
+        <v>266</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J104" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>203</v>
+        <v>369</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="J105" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>213</v>
+        <v>57</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>112</v>
+        <v>236</v>
       </c>
       <c r="J106" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -5421,215 +5422,185 @@
         <v>373</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>382</v>
+        <v>234</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>383</v>
+        <v>195</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F107" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>374</v>
+      </c>
       <c r="G107" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>188</v>
+        <v>127</v>
       </c>
       <c r="J107" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>385</v>
+        <v>257</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>198</v>
+        <v>69</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="J108" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>293</v>
+        <v>378</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>234</v>
+        <v>111</v>
       </c>
       <c r="J109" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>390</v>
+        <v>62</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>257</v>
+        <v>381</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>391</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="J110" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>290</v>
+        <v>383</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="J111" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>64</v>
+        <v>386</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>198</v>
+        <v>388</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J112" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J113" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J113"/>
+  <autoFilter ref="A1:J112"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5742,7 +5713,6 @@
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
     <hyperlink ref="H112" r:id="rId111"/>
-    <hyperlink ref="H113" r:id="rId112"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5750,9 +5720,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5761,36 +5731,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>197</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>198</v>
+        <v>69</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5798,296 +5768,334 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>64</v>
+        <v>237</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>266</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>265</v>
+        <v>184</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>330</v>
+        <v>234</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>71</v>
+        <v>195</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>332</v>
+        <v>203</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>333</v>
+        <v>224</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>334</v>
+        <v>195</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>141</v>
+        <v>339</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>198</v>
+        <v>341</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>373</v>
+        <v>266</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>374</v>
+        <v>251</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>203</v>
+        <v>349</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>64</v>
+        <v>266</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>396</v>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G19"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6105,6 +6113,8 @@
     <hyperlink ref="G15" r:id="rId14"/>
     <hyperlink ref="G16" r:id="rId15"/>
     <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6118,31 +6128,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B4" s="3">
         <v>21</v>
@@ -6150,15 +6160,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>402</v>
+        <v>239</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B6" s="3">
         <v>18</v>
@@ -6166,7 +6176,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="B7" s="3">
         <v>15</v>
@@ -6174,15 +6184,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>353</v>
+        <v>176</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>177</v>
+        <v>374</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -6190,15 +6200,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -6206,15 +6216,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -6222,7 +6232,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6230,18 +6240,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6251,21 +6261,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -6273,15 +6283,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -6289,7 +6299,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6297,7 +6307,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6305,7 +6315,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6313,7 +6323,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>257</v>
+        <v>158</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6321,15 +6331,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>70</v>
+        <v>191</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6337,7 +6347,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6345,7 +6355,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6353,7 +6363,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6361,7 +6371,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6369,7 +6379,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6377,7 +6387,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>368</v>
+        <v>251</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6391,23 +6401,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
@@ -6415,13 +6425,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3">
-        <v>22.7</v>
+        <v>19.2</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -6429,13 +6439,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -6443,13 +6453,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
-        <v>19.2</v>
+        <v>17.3</v>
       </c>
       <c r="D4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6457,10 +6467,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3">
-        <v>10.9</v>
+        <v>14.3</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -6471,10 +6481,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="C6" s="3">
-        <v>8.8</v>
+        <v>10.9</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -6485,13 +6495,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C7" s="3">
-        <v>7.3</v>
+        <v>8.8</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6499,10 +6509,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C8" s="3">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6513,10 +6523,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="C9" s="3">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="D9" s="3">
         <v>4</v>
@@ -6527,10 +6537,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="C10" s="3">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -6541,13 +6551,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="C11" s="3">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6555,13 +6565,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="C12" s="3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6569,13 +6579,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>142</v>
+        <v>227</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6583,13 +6593,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>368</v>
+        <v>141</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6597,7 +6607,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C15" s="3">
         <v>2.6</v>
@@ -6611,7 +6621,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -6634,46 +6644,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>406</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -6689,23 +6699,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -6713,7 +6723,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -6721,41 +6731,33 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6768,8 +6770,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -6780,34 +6782,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6815,31 +6817,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -6847,31 +6849,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4">
@@ -6879,31 +6881,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F4" s="3">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>304</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
@@ -6911,31 +6913,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F5" s="3">
+        <v>84</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="F5" s="3">
-        <v>68</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>435</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
@@ -6943,31 +6945,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -6975,31 +6977,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>159</v>
+        <v>437</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="F7" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -7007,31 +7009,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>432</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="F8" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>76</v>
+        <v>442</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -7039,31 +7041,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>445</v>
+        <v>72</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>291</v>
+        <v>68</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>198</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F9" s="3">
         <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>447</v>
+        <v>74</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -7071,31 +7073,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>257</v>
+        <v>445</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>203</v>
+        <v>446</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F10" s="3">
         <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -7103,31 +7105,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F11" s="3">
+        <v>44</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F11" s="3">
-        <v>40</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>455</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -7135,31 +7137,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>457</v>
+        <v>234</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="F12" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -7167,31 +7169,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>130</v>
+        <v>456</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>461</v>
+        <v>217</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F13" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14">
@@ -7199,31 +7201,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>286</v>
+        <v>195</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="F14" s="3">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15">
@@ -7231,31 +7233,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="F15" s="3">
+        <v>32</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F15" s="3">
-        <v>28</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>471</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>472</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -7263,31 +7265,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>455</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17">
@@ -7295,31 +7297,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>478</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>198</v>
+        <v>474</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F17" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18">
@@ -7327,31 +7329,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>481</v>
+        <v>417</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
@@ -7359,31 +7361,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="F19" s="3">
+        <v>28</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="F19" s="3">
-        <v>26</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -7391,31 +7393,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>490</v>
+        <v>238</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F20" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>124</v>
+        <v>459</v>
       </c>
     </row>
     <row r="21">
@@ -7423,31 +7425,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>180</v>
+        <v>490</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W26.xlsx
+++ b/reports/devops-jobs-israel-2026-W26.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-24T09:47:41</t>
+    <t xml:space="preserve">2026-06-25T09:38:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -276,15 +276,6 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
-    <t xml:space="preserve">Director of AI Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
-  </si>
-  <si>
     <t xml:space="preserve">Professional Services DevOps Architect</t>
   </si>
   <si>
@@ -456,927 +447,885 @@
     <t xml:space="preserve">Riskified</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587301002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lisbon</t>
   </si>
   <si>
     <t xml:space="preserve">Israel (other)</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4430717128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aws-devops-engineer-at-abra-4430316804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-datateam-4401758476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharpies PRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sharpies-pro-4431207225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist (36628)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432255575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4432560554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razor Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4432547601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4430560470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer%C2%A0-aws-at-comblack-4431673887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noma Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-logica-it-4429449489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stepscale.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-platform-engineer-at-stepscale-io-4432091419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-log-on-software-4429843837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4429458777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4431218841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer [Contracting]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory Ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-contracting-at-theory-ventures-4432553221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT lab Infrastructure Engineer – Cisco Silicon One</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-lab-infrastructure-engineer-%E2%80%93-cisco-silicon-one-at-cisco-4413054863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4429338126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4432202668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM &amp; System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpticSolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/pm-system-engineer-at-opticsolution-4431848577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4430717128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aws-devops-engineer-at-abra-4430316804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharpies PRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sharpies-pro-4431207225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razor Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4432510401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-logica-it-4429449489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4432276748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4430560470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4428586431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aran R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pardes Hana-Karkur, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-aran-r-d-4429840108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer [Contracting]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theory Ventures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-contracting-at-theory-ventures-4432553221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4431766041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Security - AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-security-ai-platform-engineer-at-cato-networks-4416844175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4409726747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer%C2%A0-aws-at-comblack-4431673887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noma Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4429458777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teva Pharmaceuticals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Maternity Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-maternity-leave-replacement-at-earnix-4431370720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4429373530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (533457)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-533457-at-malamteam-4429959988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4431715362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experience Linux Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galil Software Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experience-linux-engineer-at-galil-software-ltd-4430379128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4431218841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4432202668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-Fend Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-d-fend-solutions-4429992083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NoTraffic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-notraffic-4430412124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JFrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-cloud-architect-at-jfrog-4428560936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founding Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stepscale.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-platform-engineer-at-stepscale-io-4432091419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-engineer-devops-at-teads-4431209410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
@@ -1386,6 +1335,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Engineer - Intern position</t>
   </si>
   <si>
@@ -1401,105 +1359,60 @@
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Product Operations – Part-Time Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finout</t>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristocrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-product-operations-%E2%80%93-part-time-student-at-finout-4427681349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aristocrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1522,12 +1435,6 @@
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1679,7 +1586,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -1687,7 +1594,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1695,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1703,7 +1610,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>734</v>
+        <v>746</v>
       </c>
     </row>
     <row r="10">
@@ -1775,7 +1682,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1783,7 +1690,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1802,46 +1709,38 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="B6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1858,55 +1757,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>494</v>
+        <v>465</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>496</v>
+        <v>467</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>497</v>
+        <v>468</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>498</v>
+        <v>378</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
@@ -1914,55 +1813,55 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>395</v>
+        <v>469</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>499</v>
+        <v>333</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>239</v>
+        <v>470</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>500</v>
+        <v>471</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>185</v>
+        <v>372</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>501</v>
+        <v>178</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1970,18 +1869,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>502</v>
+        <v>373</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2006,13 +1905,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>503</v>
+        <v>472</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>505</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2">
@@ -2020,13 +1919,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2035,88 +1934,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3">
-        <v>33.8</v>
+        <v>34.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.0</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.0</v>
+        <v>2.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.9</v>
+        <v>32.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.5</v>
+        <v>17.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2200,7 +2099,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -2232,7 +2131,7 @@
         <v>43</v>
       </c>
       <c r="J3" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -2264,7 +2163,7 @@
         <v>47</v>
       </c>
       <c r="J4" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -2296,7 +2195,7 @@
         <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -2328,7 +2227,7 @@
         <v>47</v>
       </c>
       <c r="J6" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2360,7 +2259,7 @@
         <v>47</v>
       </c>
       <c r="J7" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -2392,7 +2291,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -2424,7 +2323,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -2456,7 +2355,7 @@
         <v>40</v>
       </c>
       <c r="J10" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -2488,7 +2387,7 @@
         <v>40</v>
       </c>
       <c r="J11" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -2520,7 +2419,7 @@
         <v>75</v>
       </c>
       <c r="J12" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -2552,7 +2451,7 @@
         <v>79</v>
       </c>
       <c r="J13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2584,7 +2483,7 @@
         <v>40</v>
       </c>
       <c r="J14" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -2601,7 +2500,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>86</v>
@@ -2613,53 +2512,53 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J15" s="3">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="J16" s="3">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>57</v>
@@ -2677,50 +2576,50 @@
         <v>95</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="J17" s="3">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J18" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>57</v>
@@ -2744,15 +2643,15 @@
         <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>57</v>
@@ -2764,27 +2663,27 @@
         <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J20" s="3">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>57</v>
@@ -2796,19 +2695,19 @@
         <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="J21" s="3">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -2816,7 +2715,7 @@
         <v>112</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>57</v>
@@ -2837,10 +2736,10 @@
         <v>114</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="J22" s="3">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -2848,10 +2747,10 @@
         <v>115</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>57</v>
@@ -2860,30 +2759,30 @@
         <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="J23" s="3">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>57</v>
@@ -2892,152 +2791,152 @@
         <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J24" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J25" s="3">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="J26" s="3">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="J27" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J28" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>141</v>
@@ -3061,18 +2960,18 @@
         <v>143</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="J29" s="3">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>145</v>
@@ -3081,7 +2980,7 @@
         <v>146</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>147</v>
@@ -3093,24 +2992,24 @@
         <v>148</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="J30" s="3">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>37</v>
@@ -3128,7 +3027,7 @@
         <v>40</v>
       </c>
       <c r="J31" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
@@ -3139,7 +3038,7 @@
         <v>154</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>57</v>
@@ -3148,30 +3047,30 @@
         <v>37</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="J32" s="3">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>57</v>
@@ -3189,51 +3088,51 @@
         <v>161</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="J33" s="3">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>57</v>
+        <v>164</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J34" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>57</v>
@@ -3242,92 +3141,92 @@
         <v>37</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="J35" s="3">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>171</v>
+        <v>57</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J36" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="J37" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>57</v>
@@ -3340,50 +3239,48 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J38" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>187</v>
+        <v>43</v>
       </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>188</v>
@@ -3405,54 +3302,54 @@
         <v>190</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>43</v>
+        <v>191</v>
       </c>
       <c r="J40" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="J41" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>58</v>
@@ -3462,24 +3359,24 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>57</v>
@@ -3495,21 +3392,21 @@
         <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>146</v>
@@ -3522,24 +3419,24 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>57</v>
@@ -3547,34 +3444,32 @@
       <c r="E45" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="I45" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>58</v>
@@ -3584,10 +3479,10 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="J46" s="3">
         <v>1</v>
@@ -3595,13 +3490,13 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>57</v>
@@ -3610,7 +3505,7 @@
         <v>58</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>22</v>
@@ -3619,10 +3514,10 @@
         <v>211</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="J47" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3633,15 +3528,17 @@
         <v>213</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F48" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
@@ -3649,10 +3546,10 @@
         <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
@@ -3663,37 +3560,37 @@
         <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>218</v>
+        <v>57</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>57</v>
@@ -3706,114 +3603,116 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J52" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J53" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>57</v>
@@ -3826,53 +3725,51 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J54" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>239</v>
-      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>189</v>
@@ -3881,63 +3778,63 @@
         <v>57</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F56" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="J56" s="3">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="I57" s="3" t="s">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="J57" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>246</v>
+        <v>62</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>57</v>
@@ -3950,54 +3847,56 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>62</v>
+        <v>246</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>57</v>
@@ -4010,40 +3909,40 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="J61" s="3">
         <v>2</v>
@@ -4051,10 +3950,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>62</v>
+        <v>252</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>189</v>
@@ -4063,31 +3962,31 @@
         <v>57</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="J62" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>57</v>
@@ -4100,87 +3999,87 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="J64" s="3">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>140</v>
+        <v>261</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>262</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>263</v>
+        <v>183</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>264</v>
+        <v>57</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>165</v>
+        <v>43</v>
       </c>
       <c r="J65" s="3">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>264</v>
+        <v>146</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>58</v>
@@ -4190,27 +4089,27 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>58</v>
@@ -4220,40 +4119,42 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>272</v>
+        <v>185</v>
       </c>
       <c r="J67" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>273</v>
+        <v>208</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F68" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="J68" s="3">
         <v>1</v>
@@ -4261,13 +4162,13 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>57</v>
@@ -4280,27 +4181,27 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="J69" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>57</v>
+        <v>275</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>37</v>
@@ -4310,24 +4211,24 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>140</v>
+        <v>277</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>146</v>
@@ -4340,84 +4241,88 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>264</v>
+        <v>57</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F73" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>291</v>
+        <v>43</v>
       </c>
       <c r="J73" s="3">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>57</v>
@@ -4430,27 +4335,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>43</v>
+        <v>232</v>
       </c>
       <c r="J74" s="3">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>191</v>
+        <v>289</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>295</v>
+        <v>183</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>37</v>
@@ -4460,24 +4365,24 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>245</v>
+        <v>158</v>
       </c>
       <c r="J75" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>140</v>
+        <v>291</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>57</v>
@@ -4490,21 +4395,21 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="J76" s="3">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>220</v>
+        <v>295</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>189</v>
@@ -4520,24 +4425,24 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>272</v>
+        <v>108</v>
       </c>
       <c r="J77" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>146</v>
@@ -4550,27 +4455,27 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>264</v>
+        <v>57</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>58</v>
@@ -4580,119 +4485,117 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>305</v>
+        <v>174</v>
       </c>
       <c r="J79" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>189</v>
+        <v>302</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>309</v>
+        <v>62</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="J81" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>55</v>
+        <v>307</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>205</v>
-      </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="J82" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>264</v>
+        <v>146</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>58</v>
@@ -4702,121 +4605,117 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>234</v>
+        <v>313</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>205</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>62</v>
+        <v>309</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>195</v>
+        <v>315</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="J85" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>321</v>
+        <v>62</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>184</v>
+        <v>318</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>146</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>185</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>181</v>
+        <v>320</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="D87" s="3" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>58</v>
@@ -4829,10 +4728,10 @@
         <v>324</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4840,45 +4739,43 @@
         <v>325</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>227</v>
+        <v>326</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>189</v>
+        <v>327</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>205</v>
-      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="J88" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>195</v>
+        <v>315</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>58</v>
@@ -4888,72 +4785,72 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>62</v>
+        <v>331</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>333</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>203</v>
+        <v>335</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>224</v>
+        <v>336</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>195</v>
+        <v>337</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>205</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4961,10 +4858,10 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>334</v>
+        <v>230</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>189</v>
@@ -4975,17 +4872,15 @@
       <c r="E92" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>205</v>
-      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>123</v>
+        <v>232</v>
       </c>
       <c r="J92" s="3">
         <v>6</v>
@@ -4993,13 +4888,13 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>57</v>
@@ -5007,231 +4902,229 @@
       <c r="E93" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>205</v>
-      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="J93" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>341</v>
+        <v>183</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>195</v>
+        <v>349</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>57</v>
+        <v>164</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="J95" s="3">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>346</v>
+        <v>55</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>218</v>
+        <v>57</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="J96" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>266</v>
+        <v>353</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>251</v>
+        <v>354</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>349</v>
+        <v>183</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="J98" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>197</v>
+        <v>362</v>
       </c>
       <c r="J99" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>356</v>
+        <v>62</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>352</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="J100" s="3">
         <v>2</v>
@@ -5239,368 +5132,66 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>266</v>
+        <v>365</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>361</v>
+        <v>65</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>234</v>
+        <v>368</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="J102" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J103" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J104" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J105" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J106" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J107" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J108" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J109" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J110" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J111" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J112" s="3">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J112"/>
+  <autoFilter ref="A1:J102"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5703,16 +5294,6 @@
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
     <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
-    <hyperlink ref="H104" r:id="rId103"/>
-    <hyperlink ref="H105" r:id="rId104"/>
-    <hyperlink ref="H106" r:id="rId105"/>
-    <hyperlink ref="H107" r:id="rId106"/>
-    <hyperlink ref="H108" r:id="rId107"/>
-    <hyperlink ref="H109" r:id="rId108"/>
-    <hyperlink ref="H110" r:id="rId109"/>
-    <hyperlink ref="H111" r:id="rId110"/>
-    <hyperlink ref="H112" r:id="rId111"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5720,9 +5301,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5754,32 +5335,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5787,18 +5368,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5806,18 +5387,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5825,18 +5406,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5844,18 +5425,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5863,18 +5444,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>246</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5882,18 +5463,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>268</v>
+        <v>189</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5901,18 +5482,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>140</v>
+        <v>307</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>301</v>
+        <v>196</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5920,18 +5501,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5939,18 +5520,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5958,18 +5539,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>318</v>
+        <v>55</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>234</v>
+        <v>351</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5977,125 +5558,11 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>385</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6109,12 +5576,6 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6128,31 +5589,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="B4" s="3">
         <v>21</v>
@@ -6160,7 +5621,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>373</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
@@ -6168,23 +5629,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>352</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>176</v>
+        <v>333</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -6192,7 +5653,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -6200,15 +5661,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -6216,15 +5677,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -6232,7 +5693,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6240,7 +5701,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6248,7 +5709,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6261,7 +5722,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6270,7 +5731,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -6283,7 +5744,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -6291,23 +5752,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>234</v>
+        <v>56</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6315,7 +5776,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6323,23 +5784,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6347,7 +5808,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6355,7 +5816,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6363,7 +5824,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6371,7 +5832,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6379,7 +5840,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6387,7 +5848,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6408,16 +5869,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -6425,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" s="3">
         <v>19.2</v>
@@ -6439,13 +5900,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3">
-        <v>18.9</v>
+        <v>17.3</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -6453,13 +5914,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3">
-        <v>17.3</v>
+        <v>15.1</v>
       </c>
       <c r="D4" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -6495,13 +5956,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C7" s="3">
-        <v>8.8</v>
+        <v>7.3</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6509,10 +5970,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C8" s="3">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6523,13 +5984,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="C9" s="3">
-        <v>6.7</v>
+        <v>5.0</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6537,13 +5998,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>129</v>
+        <v>230</v>
       </c>
       <c r="C10" s="3">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6551,7 +6012,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C11" s="3">
         <v>4.3</v>
@@ -6565,13 +6026,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="C12" s="3">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6579,13 +6040,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>227</v>
+        <v>138</v>
       </c>
       <c r="C13" s="3">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6593,10 +6054,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C14" s="3">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -6607,13 +6068,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="C15" s="3">
         <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6621,7 +6082,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -6647,21 +6108,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3">
@@ -6669,10 +6130,10 @@
         <v>58</v>
       </c>
       <c r="B3" s="3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4">
@@ -6683,7 +6144,7 @@
         <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -6702,7 +6163,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -6710,7 +6171,7 @@
         <v>57</v>
       </c>
       <c r="B2" s="3">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -6718,7 +6179,7 @@
         <v>146</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6726,20 +6187,20 @@
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>264</v>
+        <v>164</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6747,15 +6208,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6770,8 +6231,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -6782,10 +6243,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6797,10 +6258,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6817,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>81</v>
@@ -6826,19 +6287,19 @@
         <v>82</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>43</v>
@@ -6849,31 +6310,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4">
@@ -6881,31 +6342,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>201</v>
+        <v>274</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="F4" s="3">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
@@ -6913,31 +6374,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>426</v>
+        <v>331</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>427</v>
+        <v>332</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>428</v>
+        <v>177</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>429</v>
+        <v>400</v>
       </c>
       <c r="F5" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>430</v>
+        <v>407</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>431</v>
+        <v>334</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -6945,31 +6406,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="F6" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -6977,28 +6438,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="F7" s="3">
         <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>43</v>
@@ -7009,31 +6470,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>158</v>
+        <v>317</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>159</v>
+        <v>318</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="F8" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -7041,31 +6502,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>72</v>
+        <v>420</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>68</v>
+        <v>154</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="F9" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>74</v>
+        <v>422</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -7073,31 +6534,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>446</v>
+        <v>183</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="F10" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>107</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
@@ -7105,31 +6566,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>258</v>
+        <v>426</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>91</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12">
@@ -7137,31 +6598,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>234</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>43</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13">
@@ -7169,31 +6630,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>455</v>
+        <v>72</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>456</v>
+        <v>68</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>458</v>
+        <v>74</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>459</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
@@ -7201,31 +6662,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>461</v>
+        <v>230</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
       <c r="F14" s="3">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
@@ -7233,31 +6694,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>341</v>
+        <v>183</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16">
@@ -7265,31 +6726,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>469</v>
+        <v>441</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>472</v>
+        <v>444</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>305</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17">
@@ -7297,31 +6758,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>473</v>
+        <v>309</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>474</v>
+        <v>315</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="F17" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>476</v>
+        <v>316</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>477</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -7329,31 +6790,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
@@ -7361,31 +6822,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>485</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20">
@@ -7393,31 +6854,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>238</v>
+        <v>456</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>184</v>
+        <v>457</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>459</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21">
@@ -7425,31 +6886,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W26.xlsx
+++ b/reports/devops-jobs-israel-2026-W26.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-25T09:38:03</t>
+    <t xml:space="preserve">2026-06-26T09:46:18</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,12 +57,15 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
+    <t xml:space="preserve">1.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary disclosure rate %</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.0%</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary disclosure rate %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -156,30 +159,33 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
   </si>
   <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution Architect</t>
   </si>
   <si>
@@ -534,883 +540,889 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4432560554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kaltura</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharpies PRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sharpies-pro-4431207225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aws-devops-engineer-at-abra-4430316804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4433814215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist (36628)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432255575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razor Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comblack-4433308890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4432559453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4433555610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-log-on-software-4429843837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WINN.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior platform engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noma Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4429458777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Maternity Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-maternity-leave-replacement-at-earnix-4431370720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keshet Media Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer [Contracting]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory Ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-contracting-at-theory-ventures-4432553221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4433317648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4432603109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataBank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-engineer-2-databank-1134066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Software Student, Annapurna Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-software-student-annapurna-labs-at-amazon-web-services-aws-4431605549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4429863387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4430717128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aws-devops-engineer-at-abra-4430316804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-datateam-4401758476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharpies PRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sharpies-pro-4431207225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist (36628)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432255575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4432560554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razor Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4432547601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4430560470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer%C2%A0-aws-at-comblack-4431673887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noma Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-logica-it-4429449489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founding Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stepscale.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-platform-engineer-at-stepscale-io-4432091419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-log-on-software-4429843837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4429458777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4431218841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer [Contracting]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theory Ventures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-contracting-at-theory-ventures-4432553221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT lab Infrastructure Engineer – Cisco Silicon One</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-lab-infrastructure-engineer-%E2%80%93-cisco-silicon-one-at-cisco-4413054863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4429338126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4432202668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM &amp; System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpticSolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/pm-system-engineer-at-opticsolution-4431848577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aristocrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1419,22 +1431,22 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1586,7 +1598,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -1594,7 +1606,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1602,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1610,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>746</v>
+        <v>755</v>
       </c>
     </row>
     <row r="10">
@@ -1618,7 +1630,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1634,7 +1646,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1643,26 +1655,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1671,23 +1683,23 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
         <v>34</v>
@@ -1706,23 +1718,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
@@ -1730,18 +1742,18 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>463</v>
+        <v>425</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1757,18 +1769,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B2" s="3">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -1776,79 +1788,79 @@
         <v>358</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>468</v>
+        <v>376</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>378</v>
+        <v>472</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>469</v>
+        <v>321</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>333</v>
+        <v>473</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>374</v>
+        <v>474</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>471</v>
+        <v>370</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1856,31 +1868,31 @@
         <v>372</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1899,123 +1911,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>36</v>
       </c>
       <c r="C2" s="3">
-        <v>15.1</v>
+        <v>13.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3">
         <v>76</v>
       </c>
       <c r="C3" s="3">
-        <v>34.8</v>
+        <v>36.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.2</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.5</v>
+        <v>33.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>17.8</v>
+        <v>13.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2027,7 +2039,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2040,130 +2052,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="3">
         <v>42</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="3">
-        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="3">
         <v>45</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" s="3">
-        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -2171,31 +2183,31 @@
         <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -2203,1286 +2215,1286 @@
         <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J6" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="J7" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J8" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J12" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J15" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J17" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J18" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J19" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J20" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J21" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J22" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J25" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J26" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J29" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J32" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J34" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J35" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>178</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J37" s="3">
         <v>22</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J37" s="3">
-        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="J39" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="D41" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="J46" s="3">
         <v>1</v>
@@ -3490,31 +3502,29 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>208</v>
+        <v>139</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="J47" s="3">
         <v>2</v>
@@ -3522,761 +3532,757 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>69</v>
+        <v>201</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="J48" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F49" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="J51" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>229</v>
+        <v>44</v>
       </c>
       <c r="J53" s="3">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>236</v>
+        <v>59</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F55" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J56" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>242</v>
+        <v>185</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>183</v>
+        <v>247</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>57</v>
+        <v>248</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>177</v>
+        <v>252</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>146</v>
+        <v>253</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>178</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="J60" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>62</v>
+        <v>257</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>259</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J61" s="3">
         <v>22</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>252</v>
+        <v>139</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>255</v>
+        <v>139</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>180</v>
+        <v>265</v>
       </c>
       <c r="J63" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>260</v>
+        <v>177</v>
       </c>
       <c r="J64" s="3">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J65" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>264</v>
+        <v>95</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>266</v>
+        <v>201</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>191</v>
+        <v>274</v>
       </c>
       <c r="J66" s="3">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>185</v>
+        <v>44</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="J69" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>277</v>
+        <v>139</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>146</v>
+        <v>248</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="J71" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>189</v>
+        <v>289</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>57</v>
+        <v>290</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="J72" s="3">
         <v>0</v>
@@ -4284,181 +4290,183 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>283</v>
+        <v>64</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="J73" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="J74" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G75" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="J75" s="3">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>294</v>
+        <v>160</v>
       </c>
       <c r="J76" s="3">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>295</v>
+        <v>139</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="J77" s="3">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F78" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G78" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="J78" s="3">
         <v>2</v>
@@ -4466,329 +4474,335 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F79" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G79" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>302</v>
+        <v>185</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>304</v>
+        <v>225</v>
       </c>
       <c r="J80" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>62</v>
+        <v>311</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="J81" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>196</v>
+        <v>315</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>309</v>
+        <v>64</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>310</v>
+        <v>178</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>302</v>
+        <v>179</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F84" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="G84" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>315</v>
+        <v>201</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>62</v>
+        <v>319</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>318</v>
+        <v>192</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F86" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="G86" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="J86" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>323</v>
+        <v>201</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>236</v>
+        <v>59</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>327</v>
+        <v>201</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>329</v>
+        <v>211</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>315</v>
+        <v>192</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="J89" s="3">
         <v>1</v>
@@ -4796,402 +4810,310 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>333</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>337</v>
+        <v>201</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>185</v>
+        <v>342</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>230</v>
+        <v>344</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="J92" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>183</v>
+        <v>348</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>57</v>
+        <v>166</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="J93" s="3">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>183</v>
+        <v>352</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="J94" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>347</v>
+        <v>57</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>349</v>
+        <v>201</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F95" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G95" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="J95" s="3">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>55</v>
+        <v>356</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>210</v>
+        <v>358</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>356</v>
+        <v>183</v>
       </c>
       <c r="J97" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>358</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>124</v>
+        <v>365</v>
       </c>
       <c r="J98" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>360</v>
+        <v>64</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>317</v>
+        <v>366</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>318</v>
+        <v>201</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>362</v>
+        <v>187</v>
       </c>
       <c r="J99" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J100" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J101" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J102" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
+  <autoFilter ref="A1:J99"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5291,9 +5213,6 @@
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5301,8 +5220,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5312,257 +5231,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>177</v>
+        <v>71</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>240</v>
+        <v>139</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>242</v>
+        <v>175</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>137</v>
+        <v>287</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>177</v>
+        <v>289</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>319</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>282</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>177</v>
+        <v>71</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5573,9 +5435,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5589,15 +5448,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B2" s="3">
         <v>30</v>
@@ -5605,7 +5464,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>178</v>
+        <v>370</v>
       </c>
       <c r="B3" s="3">
         <v>22</v>
@@ -5613,23 +5472,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>372</v>
+        <v>193</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B6" s="3">
         <v>16</v>
@@ -5637,15 +5496,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>333</v>
+        <v>171</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5653,7 +5512,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5661,15 +5520,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -5677,15 +5536,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -5693,23 +5552,23 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5728,15 +5587,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -5744,7 +5603,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5752,7 +5611,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5760,7 +5619,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5768,7 +5627,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5776,7 +5635,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5784,7 +5643,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5792,7 +5651,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5800,7 +5659,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5808,7 +5667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5816,7 +5675,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5824,7 +5683,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5832,7 +5691,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5840,7 +5699,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5848,10 +5707,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5862,23 +5721,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
@@ -5886,13 +5745,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="D2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -5900,13 +5759,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3">
-        <v>17.3</v>
+        <v>19.2</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -5914,7 +5773,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="3">
         <v>15.1</v>
@@ -5928,7 +5787,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" s="3">
         <v>14.3</v>
@@ -5942,7 +5801,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3">
         <v>10.9</v>
@@ -5956,7 +5815,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C7" s="3">
         <v>7.3</v>
@@ -5970,7 +5829,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C8" s="3">
         <v>6.2</v>
@@ -5984,7 +5843,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C9" s="3">
         <v>5.0</v>
@@ -5998,13 +5857,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="C10" s="3">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6012,13 +5871,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="C11" s="3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6026,7 +5885,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C12" s="3">
         <v>3.1</v>
@@ -6040,7 +5899,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C13" s="3">
         <v>2.9</v>
@@ -6054,7 +5913,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C14" s="3">
         <v>2.6</v>
@@ -6068,10 +5927,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6082,10 +5941,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6105,46 +5964,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>387</v>
+        <v>259</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>388</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -6160,31 +6019,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B2" s="3">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6192,7 +6051,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -6200,7 +6059,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6208,17 +6067,25 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>134</v>
+        <v>253</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6243,34 +6110,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6278,31 +6145,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -6310,31 +6177,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>398</v>
+        <v>257</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>399</v>
+        <v>258</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>402</v>
+        <v>260</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>260</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -6342,31 +6209,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F4" s="3">
-        <v>88</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5">
@@ -6374,31 +6241,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F5" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -6406,31 +6273,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F6" s="3">
+        <v>74</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F6" s="3">
-        <v>76</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>79</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7">
@@ -6438,31 +6305,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F7" s="3">
+        <v>64</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="F7" s="3">
-        <v>57</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>416</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
@@ -6470,31 +6337,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" s="3">
+        <v>57</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>52</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>419</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -6502,31 +6369,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F9" s="3">
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -6534,31 +6401,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>420</v>
+        <v>74</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>423</v>
+        <v>70</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>421</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>424</v>
+        <v>76</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>320</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -6566,31 +6433,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="F11" s="3">
+        <v>44</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F11" s="3">
-        <v>47</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>428</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>429</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -6598,31 +6465,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F12" s="3">
+        <v>40</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F12" s="3">
-        <v>47</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>433</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>362</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -6630,19 +6497,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>72</v>
+        <v>432</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>68</v>
+        <v>433</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>69</v>
+        <v>201</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>434</v>
@@ -6651,10 +6518,10 @@
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>74</v>
+        <v>435</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>75</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14">
@@ -6662,31 +6529,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>230</v>
+        <v>437</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -6694,31 +6561,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
@@ -6726,31 +6593,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>274</v>
+        <v>446</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>445</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -6758,31 +6625,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>309</v>
+        <v>396</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>271</v>
+        <v>449</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>316</v>
+        <v>451</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>79</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18">
@@ -6790,31 +6657,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F18" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>79</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19">
@@ -6822,31 +6689,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>452</v>
+        <v>255</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>356</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20">
@@ -6854,31 +6721,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>457</v>
+        <v>201</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F20" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>362</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21">
@@ -6886,31 +6753,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>460</v>
+        <v>191</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W26.xlsx
+++ b/reports/devops-jobs-israel-2026-W26.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="491">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-26T09:46:18</t>
+    <t xml:space="preserve">2026-06-28T09:26:13</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -159,10 +159,13 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
     <t xml:space="preserve">Lead DevOps Engineer</t>
@@ -177,15 +180,9 @@
     <t xml:space="preserve">Senior Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution Architect</t>
   </si>
   <si>
@@ -591,862 +588,883 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS DevOps Engineer</t>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4433814215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (35679)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-35679-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434278425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4434266248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4432547601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-log-on-software-4429843837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comblack-4433308890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noma Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4430658020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Maternity Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-maternity-leave-replacement-at-earnix-4431370720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yaqum, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-youcc-technologies-ltd-4431677475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tl-at-nova-ltd-4430216198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stepscale.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-platform-engineer-at-stepscale-io-4432091419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WINN.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grip Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-data-platform-engineer-at-grip-security-4433092160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4429458777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyx Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-onyx-security-4433485039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMOS-Spacecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-amos-spacecom-4430211390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4431218841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer [Contracting]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory Ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-contracting-at-theory-ventures-4432553221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434276396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4432202668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4434284102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experience Linux Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galil Software Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experience-linux-engineer-at-galil-software-ltd-4430379128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM &amp; System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpticSolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/pm-system-engineer-at-opticsolution-4431848577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior platform engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataBank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-engineer-2-databank-1134066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4433317648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aws-devops-engineer-at-abra-4430316804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4433814215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist (36628)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432255575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razor Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-team-lead-at-razor-labs-4431373956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comblack-4433308890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4432559453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-devops-engineer-at-intel-4430330413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4433555610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-log-on-software-4429843837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amarel-ltd-4418248357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINN.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior platform engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noma Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4429458777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4428940001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Maternity Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-maternity-leave-replacement-at-earnix-4431370720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keshet Media Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-keshet-media-group-4417611355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer [Contracting]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theory Ventures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-contracting-at-theory-ventures-4432553221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4433317648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4432603109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataBank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-engineer-2-databank-1134066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Software Student, Annapurna Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, AWS, Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-software-student-annapurna-labs-at-amazon-web-services-aws-4431605549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4429863387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD, Git</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support - Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontegg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Azure, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-frontegg-4421806900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-student-at-rapyd-4428700406</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1598,7 +1616,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -1606,7 +1624,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1614,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -1622,7 +1640,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>755</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10">
@@ -1694,7 +1712,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1721,36 +1739,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>425</v>
+        <v>458</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1769,39 +1787,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>469</v>
+        <v>379</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
@@ -1809,90 +1827,90 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>376</v>
+        <v>477</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>472</v>
+        <v>383</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>321</v>
+        <v>478</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>474</v>
+        <v>378</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>193</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>371</v>
+        <v>481</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1917,13 +1935,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2">
@@ -1934,10 +1952,10 @@
         <v>36</v>
       </c>
       <c r="C2" s="3">
-        <v>13.5</v>
+        <v>15.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1946,88 +1964,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3">
-        <v>36.6</v>
+        <v>32.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.3</v>
+        <v>8.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.1</v>
+        <v>29.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>13.9</v>
+        <v>15.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2039,8 +2057,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2111,7 +2129,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -2143,7 +2161,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -2172,15 +2190,15 @@
         <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>35</v>
@@ -2195,24 +2213,24 @@
         <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>35</v>
@@ -2227,7 +2245,7 @@
         <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
@@ -2236,15 +2254,15 @@
         <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J6" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>35</v>
@@ -2259,627 +2277,627 @@
         <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J7" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="J8" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="J12" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J13" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="J15" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="J17" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="J18" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="J19" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="J20" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J21" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J22" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J23" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="J24" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J25" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J26" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -2887,237 +2905,237 @@
         <v>45</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J29" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="D32" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="J32" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>38</v>
@@ -3127,224 +3145,222 @@
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="J34" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J35" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="D36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J37" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="J38" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="D39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J40" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="I41" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J41" s="3">
         <v>5</v>
@@ -3352,263 +3368,261 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J42" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>204</v>
+        <v>138</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="J44" s="3">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F46" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="J47" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="I48" s="3" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="J48" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="J49" s="3">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="D50" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
@@ -3618,7 +3632,7 @@
         <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="J50" s="3">
         <v>4</v>
@@ -3626,49 +3640,49 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="D51" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="C52" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
@@ -3678,24 +3692,24 @@
         <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="C53" s="3" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -3705,27 +3719,27 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="J53" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="D54" s="3" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>38</v>
@@ -3738,30 +3752,30 @@
         <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="C55" s="3" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="F55" s="3" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>23</v>
@@ -3770,89 +3784,89 @@
         <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>239</v>
+        <v>89</v>
       </c>
       <c r="J55" s="3">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>57</v>
+        <v>239</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>217</v>
-      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>90</v>
+        <v>244</v>
       </c>
       <c r="J56" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>248</v>
+        <v>147</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
@@ -3862,10 +3876,10 @@
         <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3873,283 +3887,283 @@
         <v>250</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>253</v>
+        <v>147</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>259</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="J61" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>139</v>
+        <v>259</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>263</v>
+        <v>174</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="J63" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>266</v>
+        <v>94</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="J65" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="J66" s="3">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D67" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="J67" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4159,239 +4173,237 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J68" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>175</v>
+        <v>277</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>64</v>
+        <v>279</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>252</v>
+        <v>194</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>253</v>
+        <v>58</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>139</v>
+        <v>282</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>248</v>
+        <v>147</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J71" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>64</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>201</v>
+        <v>291</v>
       </c>
       <c r="D73" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J73" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J75" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>299</v>
+        <v>145</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>38</v>
@@ -4401,365 +4413,363 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="J76" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="D77" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E77" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J77" s="3">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>217</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>217</v>
-      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>139</v>
+        <v>305</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>225</v>
+        <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D82" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="J82" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>178</v>
+        <v>314</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>318</v>
+        <v>244</v>
       </c>
       <c r="J83" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>319</v>
+        <v>138</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>321</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>323</v>
+        <v>138</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D85" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>54</v>
+        <v>320</v>
       </c>
       <c r="J85" s="3">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>321</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D87" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="J87" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>38</v>
@@ -4769,70 +4779,70 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J88" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>337</v>
+        <v>209</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J90" s="3">
         <v>0</v>
@@ -4840,59 +4850,59 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="D91" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="J91" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>71</v>
+        <v>337</v>
       </c>
       <c r="D92" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J92" s="3">
         <v>0</v>
@@ -4900,170 +4910,172 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>348</v>
+        <v>210</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="J93" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>352</v>
+        <v>226</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F94" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="J94" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>57</v>
+        <v>346</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D95" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="F95" s="3" t="s">
-        <v>217</v>
+        <v>342</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>185</v>
+        <v>351</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>358</v>
-      </c>
+      <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="J96" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D97" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="J97" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>178</v>
+        <v>356</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>38</v>
@@ -5073,27 +5085,27 @@
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>365</v>
+        <v>44</v>
       </c>
       <c r="J98" s="3">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>64</v>
+        <v>358</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>38</v>
@@ -5103,17 +5115,139 @@
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="J99" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J100" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J101" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="I99" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J99" s="3">
-        <v>3</v>
+      <c r="B102" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J102" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J103" s="3">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J103"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5213,6 +5347,10 @@
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5220,8 +5358,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5254,13 +5392,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5268,18 +5406,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5287,18 +5425,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>234</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5306,18 +5444,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5325,18 +5463,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>139</v>
+        <v>271</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5344,18 +5482,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>287</v>
+        <v>145</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>289</v>
+        <v>184</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5363,18 +5501,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>319</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5382,18 +5520,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5401,18 +5539,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>344</v>
+        <v>209</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>71</v>
+        <v>226</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5420,11 +5558,49 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>345</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5435,6 +5611,8 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5448,47 +5626,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>193</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B6" s="3">
         <v>16</v>
@@ -5496,15 +5674,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5512,23 +5690,23 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -5536,15 +5714,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -5552,23 +5730,23 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5590,7 +5768,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
@@ -5603,7 +5781,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5611,7 +5789,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5619,7 +5797,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5627,7 +5805,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5635,15 +5813,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5651,7 +5829,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5659,7 +5837,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5667,7 +5845,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5675,7 +5853,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5683,7 +5861,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5691,7 +5869,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5699,7 +5877,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5707,10 +5885,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>135</v>
+        <v>257</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5721,23 +5899,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
@@ -5745,13 +5923,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C2" s="3">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5759,13 +5937,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
-        <v>19.2</v>
+        <v>17.3</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -5773,7 +5951,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="3">
         <v>15.1</v>
@@ -5787,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3">
         <v>14.3</v>
@@ -5801,7 +5979,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3">
         <v>10.9</v>
@@ -5815,7 +5993,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3">
         <v>7.3</v>
@@ -5829,7 +6007,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="3">
         <v>6.2</v>
@@ -5843,7 +6021,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C9" s="3">
         <v>5.0</v>
@@ -5857,7 +6035,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10" s="3">
         <v>4.3</v>
@@ -5871,13 +6049,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="C11" s="3">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5885,13 +6063,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>232</v>
+        <v>139</v>
       </c>
       <c r="C12" s="3">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5899,13 +6077,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5913,13 +6091,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>152</v>
+        <v>257</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5927,13 +6105,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5941,7 +6119,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5967,15 +6145,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -5986,13 +6164,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4">
@@ -6000,10 +6178,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -6022,23 +6200,23 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -6051,7 +6229,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -6059,7 +6237,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>248</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6067,15 +6245,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6083,7 +6261,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6098,7 +6276,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6110,10 +6288,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6125,10 +6303,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6145,31 +6323,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>390</v>
+        <v>285</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>83</v>
+        <v>286</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>393</v>
+        <v>288</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -6177,31 +6355,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>257</v>
+        <v>399</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>400</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>260</v>
+        <v>403</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -6209,31 +6387,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>71</v>
+        <v>406</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>409</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>274</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -6241,31 +6419,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -6273,31 +6451,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>406</v>
+        <v>155</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>318</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -6305,31 +6483,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>411</v>
+        <v>194</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="F7" s="3">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>413</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
@@ -6337,31 +6515,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>415</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>416</v>
+        <v>69</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F8" s="3">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>418</v>
+        <v>75</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -6369,31 +6547,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -6401,31 +6579,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>70</v>
+        <v>303</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>71</v>
+        <v>330</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F10" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>76</v>
+        <v>331</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -6433,31 +6611,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>424</v>
+        <v>194</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -6465,31 +6643,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>294</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>429</v>
+        <v>174</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F12" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -6497,31 +6675,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F13" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">
@@ -6529,31 +6707,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>201</v>
+        <v>440</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="F14" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -6561,31 +6739,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>106</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16">
@@ -6593,31 +6771,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>445</v>
+        <v>248</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>446</v>
+        <v>215</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17">
@@ -6625,31 +6803,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>396</v>
+        <v>452</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -6657,31 +6835,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>456</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -6689,31 +6867,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>255</v>
+        <v>462</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>252</v>
+        <v>184</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>460</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
@@ -6721,31 +6899,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21">
@@ -6753,31 +6931,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>191</v>
+        <v>470</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="F21" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
